--- a/site/Active-Directory-Jira-Service-Management-Cloud-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Jira-Service-Management-Cloud-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KGP7D7WBCC634HCZ096YE333</t>
+          <t>h_01KH64RPGGM8JEMST8KRVZDG76</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Jira-Service-Management-Cloud-Integration-Guide/#h_01KGP7D7WBCC634HCZ096YE333</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Jira-Service-Management-Cloud-Integration-Guide/#h_01KH64RPGGM8JEMST8KRVZDG76</t>
         </is>
       </c>
     </row>
